--- a/output/pdf_financials_xlsx/GHR.H.xlsx
+++ b/output/pdf_financials_xlsx/GHR.H.xlsx
@@ -4533,34 +4533,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.907961</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.902217</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.918171</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.907301</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -9828,7 +9828,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -10278,7 +10282,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -10718,7 +10726,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -11462,7 +11474,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -12132,7 +12148,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.907961</v>
       </c>

--- a/output/pdf_financials_xlsx/GHR.H.xlsx
+++ b/output/pdf_financials_xlsx/GHR.H.xlsx
@@ -1943,40 +1943,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.022783</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.01773</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.014596</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.018045</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.013916</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.341876</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.284636</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.106286</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.062953</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022741</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.008635</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.129452</v>
       </c>
     </row>
     <row r="35">
@@ -2029,40 +2029,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.00696</v>
+        <v>0.029743</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.004015</v>
+        <v>0.021745</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.019969</v>
+        <v>0.034565</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.018045</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.013916</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.341876</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.284636</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.106286</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.062953</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.022741</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.008635</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.129452</v>
       </c>
     </row>
     <row r="37">
@@ -2545,40 +2545,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.031166</v>
+        <v>0.008383</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.025718</v>
+        <v>0.007988</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.018321</v>
+        <v>0.003725</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.020146</v>
+        <v>0.002101</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.013916</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.343126</v>
+        <v>0.00125</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.284636</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.106286</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.062953</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.022741</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.008635</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.129452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
